--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486418_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486418_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6733</v>
+        <v>2.2919</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3533</v>
+        <v>2.4651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.32</v>
+        <v>-0.1732</v>
       </c>
       <c r="G2" t="n">
         <v>0.2035</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1647</v>
+        <v>1.7833</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7487</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4161</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2196</v>
+        <v>1.0847</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1014</v>
+        <v>0.0103</v>
       </c>
       <c r="F3" t="n">
-        <v>1.321</v>
+        <v>1.0744</v>
       </c>
       <c r="G3" t="n">
         <v>1.4782</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3716</v>
+        <v>0.2367</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U3" t="n">
-        <v>0.702</v>
+        <v>0.4554</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1019</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6238</v>
+        <v>3.1768</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.522</v>
+        <v>-2.3678</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7413</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7779</v>
+        <v>1.485</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4937</v>
+        <v>1.0467</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2842</v>
+        <v>0.4383</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9351</v>
+        <v>-0.1798</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6791</v>
+        <v>2.1262</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6142</v>
+        <v>-2.306</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5742</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3341</v>
+        <v>1.0893</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3581</v>
+        <v>0.8051</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.024</v>
+        <v>0.2842</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9852</v>
+        <v>-1.8716</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4091</v>
+        <v>0.7385</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3943</v>
+        <v>-2.6101</v>
       </c>
       <c r="G6" t="n">
         <v>-1.8604</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0927</v>
+        <v>0.2064</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1152</v>
+        <v>0.4446</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0225</v>
+        <v>-0.2382</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9872</v>
+        <v>-2.0875</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.188</v>
+        <v>-1.4115</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7992</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6585</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5412</v>
+        <v>0.441</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6081</v>
+        <v>0.3845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3748</v>
+        <v>-2.9018</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.815</v>
+        <v>0.2536</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5599</v>
+        <v>-3.1554</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8917</v>
+        <v>2.4879</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8256</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9339</v>
+        <v>1.7093</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2075</v>
+        <v>3.4261</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3624</v>
+        <v>1.7614</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5698</v>
+        <v>1.6647</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0992</v>
+        <v>-0.9381</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4633</v>
+        <v>-0.9827</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6359</v>
+        <v>0.0446</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.305</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1781</v>
+        <v>-0.3022</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1526</v>
+        <v>0.0901</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3307</v>
+        <v>-0.3924</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>J. BERGSTEDT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4336</v>
+        <v>-3.3289</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0301</v>
+        <v>-1.5565</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4637</v>
+        <v>-1.7724</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4879</v>
+        <v>-2.6512</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7786999999999999</v>
+        <v>-1.095</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7093</v>
+        <v>-1.5563</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4261</v>
+        <v>-1.2844</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7614</v>
+        <v>0.1674</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6647</v>
+        <v>-1.4519</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9381</v>
+        <v>-1.3668</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9827</v>
+        <v>-1.2624</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0446</v>
+        <v>-0.1044</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.8276</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.834</v>
+        <v>1.2374</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1334</v>
+        <v>0.7306</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7006</v>
+        <v>0.5068</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BERGSTEDT</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6604</v>
+        <v>-3.5482</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.227</v>
+        <v>-1.9267</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4334</v>
+        <v>-1.6215</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6512</v>
+        <v>-1.8917</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.095</v>
+        <v>-2.8256</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5563</v>
+        <v>0.9339</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2844</v>
+        <v>0.2075</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1674</v>
+        <v>-1.3624</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4519</v>
+        <v>1.5698</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3668</v>
+        <v>-2.0992</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2624</v>
+        <v>-1.4633</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1044</v>
+        <v>-0.6359</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0451</v>
+        <v>-1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.906</v>
+        <v>-0.3515</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0601</v>
+        <v>0.0409</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8459</v>
+        <v>-0.3924</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7445</v>
+        <v>-4.4708</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5867</v>
+        <v>-3.2515</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1577</v>
+        <v>-1.2194</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0351</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3391</v>
+        <v>-0.0655</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1935</v>
+        <v>0.1418</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1456</v>
+        <v>-0.2073</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2108</v>
+        <v>-4.5287</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.168</v>
+        <v>-2.6092</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0428</v>
+        <v>-1.9195</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7172</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9933</v>
+        <v>-0.3112</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5924</v>
+        <v>-0.0336</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4009</v>
+        <v>-0.2776</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1952</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.9109</v>
+        <v>-10.5161</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.0914</v>
+        <v>-9.097200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8195</v>
+        <v>-1.4188</v>
       </c>
       <c r="G13" t="n">
         <v>-6.5201</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2644</v>
+        <v>1.6592</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3073</v>
+        <v>1.3015</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0429</v>
+        <v>0.3578</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.2477</v>
+        <v>-29.2478</v>
       </c>
       <c r="E14" t="n">
         <v>-11.0821</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.1657</v>
+        <v>-18.1656</v>
       </c>
       <c r="G14" t="n">
         <v>-18.4801</v>
@@ -1522,7 +1522,7 @@
         <v>3.5118</v>
       </c>
       <c r="K14" t="n">
-        <v>1.523199999999999</v>
+        <v>1.5232</v>
       </c>
       <c r="L14" t="n">
         <v>1.9883</v>
@@ -1543,16 +1543,16 @@
         <v>-22.8382</v>
       </c>
       <c r="R14" t="n">
-        <v>7.612500000000001</v>
+        <v>7.6125</v>
       </c>
       <c r="S14" t="n">
-        <v>7.1081</v>
+        <v>7.107900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>5.594</v>
+        <v>5.5939</v>
       </c>
       <c r="U14" t="n">
-        <v>1.514200000000001</v>
+        <v>1.514</v>
       </c>
       <c r="V14" t="n">
         <v>-2.6503</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5259</v>
+        <v>6.49</v>
       </c>
       <c r="E15" t="n">
         <v>3.8255</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7004</v>
+        <v>2.6645</v>
       </c>
       <c r="G15" t="n">
         <v>2.8489</v>
@@ -1624,13 +1624,13 @@
         <v>3.2626</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2192</v>
+        <v>0.1833</v>
       </c>
       <c r="T15" t="n">
         <v>0.0601</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1591</v>
+        <v>0.1232</v>
       </c>
       <c r="V15" t="n">
         <v>0.1952</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. RADONCIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9115</v>
+        <v>6.3795</v>
       </c>
       <c r="E16" t="n">
-        <v>5.035</v>
+        <v>5.1314</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8764999999999999</v>
+        <v>1.2481</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1993</v>
+        <v>5.202</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9011</v>
+        <v>5.3223</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2983</v>
+        <v>-0.1203</v>
       </c>
       <c r="J16" t="n">
-        <v>6.0625</v>
+        <v>4.9161</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4909</v>
+        <v>4.7631</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5716</v>
+        <v>0.153</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1369</v>
+        <v>0.2859</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4102</v>
+        <v>0.5592</v>
       </c>
       <c r="O16" t="n">
         <v>-0.2733</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9403</v>
+        <v>-0.91</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0601</v>
+        <v>-0.3497</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0004</v>
+        <v>-0.5603</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. RADONCIC</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8644</v>
+        <v>5.9911</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7961</v>
+        <v>4.8115</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0683</v>
+        <v>1.1796</v>
       </c>
       <c r="G17" t="n">
-        <v>5.202</v>
+        <v>6.1993</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3223</v>
+        <v>1.9011</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1203</v>
+        <v>4.2983</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9161</v>
+        <v>6.0625</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7631</v>
+        <v>1.4909</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>4.5716</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2859</v>
+        <v>0.1369</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5592</v>
+        <v>0.4102</v>
       </c>
       <c r="O17" t="n">
         <v>-0.2733</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4251</v>
+        <v>-0.8607</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1634</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7401</v>
+        <v>-0.6973</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9095</v>
+        <v>4.7733</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1234</v>
+        <v>3.8999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7861</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>2.3842</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3872</v>
+        <v>-0.5233</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6528</v>
+        <v>-0.5654</v>
       </c>
       <c r="V18" t="n">
         <v>2.2599</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.5274</v>
+        <v>4.119</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0934</v>
+        <v>2.0588</v>
       </c>
       <c r="F19" t="n">
-        <v>1.434</v>
+        <v>2.0602</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3886</v>
+        <v>1.1176</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1878</v>
+        <v>2.8834</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7992</v>
+        <v>-1.7658</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2198</v>
+        <v>1.9568</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5951</v>
+        <v>3.5983</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3754</v>
+        <v>-1.6415</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1688</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5927</v>
+        <v>-0.7149</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.1243</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>3.0451</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>3.0451</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0513</v>
+        <v>-0.4341</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8736</v>
+        <v>-0.2884</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8223</v>
+        <v>-0.1457</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9963</v>
+        <v>3.9134</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3883</v>
+        <v>2.4228</v>
       </c>
       <c r="F20" t="n">
-        <v>1.608</v>
+        <v>1.4906</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1176</v>
+        <v>3.3886</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8834</v>
+        <v>4.1878</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7658</v>
+        <v>-0.7992</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9568</v>
+        <v>2.2198</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5983</v>
+        <v>3.5951</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6415</v>
+        <v>-1.3754</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8391999999999999</v>
+        <v>1.1688</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7149</v>
+        <v>0.5927</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1243</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0451</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0451</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5568</v>
+        <v>-0.5627</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9589</v>
+        <v>0.2031</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5979</v>
+        <v>-0.7658</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0001</v>
+        <v>1.7681</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3699</v>
+        <v>0.0752</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3701</v>
+        <v>1.6929</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.108</v>
+        <v>-1.0887</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1526</v>
+        <v>-1.0066</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0446</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1197</v>
+        <v>0.0151</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1397</v>
+        <v>-0.1762</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0199</v>
+        <v>0.1912</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9882</v>
+        <v>-1.1038</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0129</v>
+        <v>-0.8304</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0247</v>
+        <v>-0.2733</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>2.6101</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2626</v>
+        <v>2.6101</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.2466</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5997</v>
+        <v>0.0601</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2909</v>
+        <v>0.1866</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5009</v>
+        <v>1.7064</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0752</v>
+        <v>0.1446</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4257</v>
+        <v>1.5618</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0887</v>
+        <v>-0.0699</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0066</v>
+        <v>-2.0892</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.08210000000000001</v>
+        <v>2.0192</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0151</v>
+        <v>0.7693</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1762</v>
+        <v>-1.3743</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1912</v>
+        <v>2.1436</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1038</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8304</v>
+        <v>-0.7149</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2733</v>
+        <v>-0.1243</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6101</v>
+        <v>2.8276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0205</v>
+        <v>-0.3335</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0601</v>
+        <v>-0.1021</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0806</v>
+        <v>-0.2313</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.4619</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0329</v>
+        <v>-0.9287</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9556</v>
+        <v>2.3907</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0699</v>
+        <v>-1.108</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0892</v>
+        <v>-1.1526</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0192</v>
+        <v>0.0446</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7693</v>
+        <v>-0.1197</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3743</v>
+        <v>-0.1397</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1436</v>
+        <v>0.0199</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.9882</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7149</v>
+        <v>-1.0129</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1243</v>
+        <v>0.0247</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>2.8276</v>
+        <v>3.2626</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0515</v>
+        <v>0.3524</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2139</v>
+        <v>0.0409</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8376</v>
+        <v>0.3115</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.3252</v>
       </c>
       <c r="X23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2748</v>
+        <v>0.605</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8636</v>
+        <v>-0.5284</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1385</v>
+        <v>1.1334</v>
       </c>
       <c r="G24" t="n">
         <v>2.1333</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2059</v>
+        <v>-0.8757</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3497</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.521</v>
+        <v>-0.5261</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9717</v>
+        <v>-2.86</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4168</v>
+        <v>-0.3051</v>
       </c>
       <c r="F25" t="n">
         <v>-2.5549</v>
@@ -2404,10 +2404,10 @@
         <v>0.6525</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.572</v>
+        <v>-0.4602</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U25" t="n">
         <v>-0.298</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2798</v>
+        <v>-2.8649</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5536</v>
+        <v>-2.4419</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7261</v>
+        <v>-0.423</v>
       </c>
       <c r="G26" t="n">
         <v>-1.735</v>
@@ -2482,13 +2482,13 @@
         <v>0.6525</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1098</v>
+        <v>-0.6949</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4933</v>
+        <v>-0.1902</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>29.2477</v>
+        <v>31.4828</v>
       </c>
       <c r="E27" t="n">
-        <v>18.1659</v>
+        <v>18.1656</v>
       </c>
       <c r="F27" t="n">
-        <v>11.0822</v>
+        <v>13.3174</v>
       </c>
       <c r="G27" t="n">
         <v>18.48</v>
@@ -2539,7 +2539,7 @@
         <v>15.9553</v>
       </c>
       <c r="L27" t="n">
-        <v>6.036300000000001</v>
+        <v>6.0363</v>
       </c>
       <c r="M27" t="n">
         <v>-3.511799999999999</v>
@@ -2560,19 +2560,19 @@
         <v>22.8381</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.108000000000001</v>
+        <v>-4.8728</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.5141</v>
+        <v>-1.5139</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.593999999999999</v>
+        <v>-3.3588</v>
       </c>
       <c r="V27" t="n">
-        <v>2.650399999999999</v>
+        <v>2.6504</v>
       </c>
       <c r="W27" t="n">
-        <v>5.300699999999999</v>
+        <v>5.3007</v>
       </c>
       <c r="X27" t="n">
         <v>-2.6503</v>
